--- a/biodiesel/povrsine_pikova_bd.xlsx
+++ b/biodiesel/povrsine_pikova_bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nastava\diplomski radovi\2024 Latinkic Darko disertacija\Tema doktorata FTIR oksidacija\rezultati biodizel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03943EF1-A907-40E6-B146-C29477766A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23042C37-1391-4646-8920-7BCA6171170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
   <si>
     <t>A2</t>
   </si>
@@ -232,6 +232,54 @@
   </si>
   <si>
     <t>ad18_3</t>
+  </si>
+  <si>
+    <t>25 sati i ne mrda. Moram ponoviti sa ovim aditivom jos barem dva puta. Ostavljeno hladno preko vikenda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prvi aditiv, oznaka na bočici 16, ali oznake merenja ad19, čisto da se razlikuje broj merenja. Grejanje 140, mešanje 4. </t>
+  </si>
+  <si>
+    <t>Zapremina: 0.9 ml. Cilj mi je dobiti što kraći ind period, da se uklapam u 24h.</t>
+  </si>
+  <si>
+    <t>ad19_0</t>
+  </si>
+  <si>
+    <t>ad19_1</t>
+  </si>
+  <si>
+    <t>Početno vreme Oct 12 10:16</t>
+  </si>
+  <si>
+    <t>ad19_2</t>
+  </si>
+  <si>
+    <t>ad19_3</t>
+  </si>
+  <si>
+    <t>ad19_4</t>
+  </si>
+  <si>
+    <t>Lepo se vidi prvi pad na 25-27h, ali i dalje je na 93%. Izgleda radi aditiv.</t>
+  </si>
+  <si>
+    <t>Ni posle 29h se nije spustilo ispod 93%. Dakle aditiv radi. Dalje trazim ind period bez aditiva.</t>
+  </si>
+  <si>
+    <t>Čisto maslinovo ulje iz flaše, 0.9 ml, 140 st, mešanje 4, bez aditiva</t>
+  </si>
+  <si>
+    <t>Početno vreme  Oct 15 12:57</t>
+  </si>
+  <si>
+    <t>petomas_0</t>
+  </si>
+  <si>
+    <t>petomas_1</t>
+  </si>
+  <si>
+    <t>petomas_2</t>
   </si>
 </sst>
 </file>
@@ -589,6 +637,282 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1029297568"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$77:$G$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.466666666666665</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.933333333333334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.433333333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$77:$H$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>87.76376907763769</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87.224065472240653</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.117673081176733</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CF4A-46DD-ABA6-3CBC6A75C221}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1037077967"/>
+        <c:axId val="1037080047"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1037077967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1037080047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1037080047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1037077967"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2652,7 +2976,330 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$87:$G$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.016666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.883333333333333</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$87:$H$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98.039605930938407</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>98.517265399542254</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>93.666036421534486</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>93.412279828838692</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DE00-4C17-92EC-56D2199D45B0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1158785200"/>
+        <c:axId val="1158787280"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1158785200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1158787280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1158787280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1158785200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2972,6 +3619,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3488,7 +4175,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4004,7 +4691,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4520,7 +5207,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5036,7 +5723,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5552,7 +6239,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6068,7 +6755,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6584,7 +7271,1039 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7390,6 +9109,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E68FEBE8-C489-4AB8-ADA9-D256905A5B8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>52386</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A39625C-3AAD-4DA8-A1FC-AD9408FCF81E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7656,7 +9447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H79"/>
+  <dimension ref="B2:H97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" customWidth="1"/>
@@ -8895,83 +10686,334 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>61</v>
-      </c>
-      <c r="C76">
-        <v>0.18545</v>
-      </c>
-      <c r="D76">
-        <v>8.2040240000000004</v>
-      </c>
-      <c r="E76">
-        <v>22.605</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1">
-        <f>F76/60</f>
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <f>E76/22.605*100</f>
-        <v>100</v>
+      <c r="B76" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C77">
-        <v>0.298678</v>
+        <v>0.18545</v>
       </c>
       <c r="D77">
-        <v>15.054848</v>
+        <v>8.2040240000000004</v>
       </c>
       <c r="E77">
-        <v>19.838999999999999</v>
+        <v>22.605</v>
       </c>
       <c r="F77">
-        <v>1288</v>
+        <v>0</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" ref="G77:G78" si="16">F77/60</f>
-        <v>21.466666666666665</v>
+        <f>F77/60</f>
+        <v>0</v>
       </c>
       <c r="H77">
-        <f t="shared" ref="H77:H78" si="17">E77/22.605*100</f>
-        <v>87.76376907763769</v>
+        <f>E77/22.605*100</f>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C78">
-        <v>0.29822399999999999</v>
+        <v>0.298678</v>
       </c>
       <c r="D78">
-        <v>15.12495</v>
+        <v>15.054848</v>
       </c>
       <c r="E78">
-        <v>19.716999999999999</v>
+        <v>19.838999999999999</v>
       </c>
       <c r="F78">
-        <v>1436</v>
+        <v>1288</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="16"/>
-        <v>23.933333333333334</v>
+        <f t="shared" ref="G78:G79" si="16">F78/60</f>
+        <v>21.466666666666665</v>
       </c>
       <c r="H78">
-        <f t="shared" si="17"/>
-        <v>87.224065472240653</v>
+        <f t="shared" ref="H78:H79" si="17">E78/22.605*100</f>
+        <v>87.76376907763769</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79">
+        <v>0.29822399999999999</v>
+      </c>
+      <c r="D79">
+        <v>15.12495</v>
+      </c>
+      <c r="E79">
+        <v>19.716999999999999</v>
+      </c>
+      <c r="F79">
+        <v>1436</v>
+      </c>
+      <c r="G79" s="1">
+        <f t="shared" si="16"/>
+        <v>23.933333333333334</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="17"/>
+        <v>87.224065472240653</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
         <v>64</v>
+      </c>
+      <c r="C80">
+        <v>0.30754500000000001</v>
+      </c>
+      <c r="D80">
+        <v>15.439640000000001</v>
+      </c>
+      <c r="E80">
+        <v>19.919</v>
+      </c>
+      <c r="F80">
+        <v>1526</v>
+      </c>
+      <c r="G80" s="1">
+        <f t="shared" ref="G80" si="18">F80/60</f>
+        <v>25.433333333333334</v>
+      </c>
+      <c r="H80">
+        <f t="shared" ref="H80" si="19">E80/22.605*100</f>
+        <v>88.117673081176733</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87">
+        <v>0.27163999999999999</v>
+      </c>
+      <c r="D87">
+        <v>13.515874999999999</v>
+      </c>
+      <c r="E87">
+        <v>20.097999999999999</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" s="1">
+        <f>F87/60</f>
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <f>E87/20.098*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88">
+        <v>0.28594599999999998</v>
+      </c>
+      <c r="D88">
+        <v>14.512459</v>
+      </c>
+      <c r="E88">
+        <v>19.704000000000001</v>
+      </c>
+      <c r="F88">
+        <v>1332</v>
+      </c>
+      <c r="G88" s="1">
+        <f>F88/60</f>
+        <v>22.2</v>
+      </c>
+      <c r="H88">
+        <f>E88/20.098*100</f>
+        <v>98.039605930938407</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89">
+        <v>0.26732299999999998</v>
+      </c>
+      <c r="D89">
+        <v>13.501348</v>
+      </c>
+      <c r="E89">
+        <v>19.8</v>
+      </c>
+      <c r="F89">
+        <v>1501</v>
+      </c>
+      <c r="G89" s="1">
+        <f>F89/60</f>
+        <v>25.016666666666666</v>
+      </c>
+      <c r="H89">
+        <f>E89/20.098*100</f>
+        <v>98.517265399542254</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>72</v>
+      </c>
+      <c r="C90">
+        <v>0.22309499999999999</v>
+      </c>
+      <c r="D90">
+        <v>11.850803000000001</v>
+      </c>
+      <c r="E90">
+        <v>18.824999999999999</v>
+      </c>
+      <c r="F90">
+        <v>1673</v>
+      </c>
+      <c r="G90" s="1">
+        <f>F90/60</f>
+        <v>27.883333333333333</v>
+      </c>
+      <c r="H90">
+        <f>E90/20.098*100</f>
+        <v>93.666036421534486</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91">
+        <v>0.23916100000000001</v>
+      </c>
+      <c r="D91">
+        <v>12.739129</v>
+      </c>
+      <c r="E91">
+        <v>18.774000000000001</v>
+      </c>
+      <c r="F91">
+        <v>1776</v>
+      </c>
+      <c r="G91" s="1">
+        <f>F91/60</f>
+        <v>29.6</v>
+      </c>
+      <c r="H91">
+        <f>E91/20.098*100</f>
+        <v>93.412279828838692</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B93" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B94" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>78</v>
+      </c>
+      <c r="C95">
+        <v>0.29269699999999998</v>
+      </c>
+      <c r="D95">
+        <v>14.670494</v>
+      </c>
+      <c r="E95">
+        <v>19.951000000000001</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <f>F95/60</f>
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <f>E95/19.951*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96">
+        <v>0.269094</v>
+      </c>
+      <c r="D96">
+        <v>13.816716</v>
+      </c>
+      <c r="E96">
+        <v>19.475999999999999</v>
+      </c>
+      <c r="F96">
+        <v>1196</v>
+      </c>
+      <c r="G96" s="1">
+        <f>F96/60</f>
+        <v>19.933333333333334</v>
+      </c>
+      <c r="H96">
+        <f>E96/19.951*100</f>
+        <v>97.619166959049664</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>80</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <f>F97/60</f>
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <f>E97/19.951*100</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
